--- a/Assets/SimpleSolitaire/Data/Categories.xlsx
+++ b/Assets/SimpleSolitaire/Data/Categories.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>ID</t>
   </si>
@@ -41,10 +41,34 @@
     <t>分类卡ID</t>
   </si>
   <si>
-    <t>分类卡或者万能卡</t>
+    <t>分类卡1001或者万能卡1002</t>
   </si>
   <si>
     <t>多语言KEY</t>
+  </si>
+  <si>
+    <t>食物</t>
+  </si>
+  <si>
+    <t>书籍</t>
+  </si>
+  <si>
+    <t>日历</t>
+  </si>
+  <si>
+    <t>电影</t>
+  </si>
+  <si>
+    <t>汉堡</t>
+  </si>
+  <si>
+    <t>动物</t>
+  </si>
+  <si>
+    <t>大洋</t>
+  </si>
+  <si>
+    <t>布料</t>
   </si>
 </sst>
 </file>
@@ -57,9 +81,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
-    <font>
-      <sz val="11"/>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -404,12 +435,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -530,141 +576,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -719,7 +768,17 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -913,25 +972,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1192,8 +1251,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="10.6923076923077" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
@@ -1225,7 +1284,98 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3" ht="17.6" spans="1:3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="17.6" spans="1:3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="17.6" spans="1:3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="17.6" spans="1:3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="17.6" spans="1:3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="17.6" spans="1:3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="17.6" spans="1:3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="17.6" spans="1:3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="C3:C10">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
